--- a/sheets/민요/검수/풍년가.xlsx
+++ b/sheets/민요/검수/풍년가.xlsx
@@ -436,10 +436,7 @@
       </patternFill>
     </fill>
     <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
+      <patternFill patternType="none"/>
     </fill>
   </fills>
   <borders count="5">

--- a/sheets/민요/검수/풍년가.xlsx
+++ b/sheets/민요/검수/풍년가.xlsx
@@ -382,17 +382,17 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
@@ -509,7 +509,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="24">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -563,6 +563,46 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3884,552 +3924,552 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+    <pageSetUpPr fitToPage="0"/>
   </sheetPr>
   <dimension ref="B1:Q14"/>
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="14" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="15" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="14" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="15" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="14" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="15" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="14" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="15" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="14" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="15" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="14" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="15" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="14" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="15" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="14" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="15" width="6"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="2" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="6" t="s">
+    <row r="1" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="6.0" customHeight="true"/>
+    <row r="2" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="68.97" customHeight="true">
+      <c r="B2" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="6"/>
-      <c r="K2" s="6"/>
-      <c r="L2" s="6"/>
-      <c r="M2" s="6"/>
-      <c r="N2" s="6"/>
-      <c r="O2" s="6"/>
-      <c r="P2" s="6"/>
-      <c r="Q2" s="6"/>
-    </row>
-    <row r="3" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="C3" s="8" t="s">
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
+      <c r="I2" s="16"/>
+      <c r="J2" s="16"/>
+      <c r="K2" s="16"/>
+      <c r="L2" s="16"/>
+      <c r="M2" s="16"/>
+      <c r="N2" s="16"/>
+      <c r="O2" s="16"/>
+      <c r="P2" s="16"/>
+      <c r="Q2" s="16"/>
+    </row>
+    <row r="3" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+      <c r="B3" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="C3" s="18" t="s">
         <v>101</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="18" t="s">
         <v>94</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="G3" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="I3" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="J3" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="K3" s="8" t="s">
+      <c r="J3" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="K3" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="L3" s="7" t="s">
+      <c r="L3" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="M3" s="8" t="s">
+      <c r="M3" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="N3" s="7" t="s">
+      <c r="N3" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="O3" s="8" t="s">
+      <c r="O3" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="P3" s="7" t="s">
+      <c r="P3" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="Q3" s="8" t="s">
+      <c r="Q3" s="18" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="C4" s="9" t="s">
+    <row r="4" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+      <c r="B4" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="C4" s="19" t="s">
         <v>102</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="E4" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="G4" s="9"/>
-      <c r="H4" s="7"/>
-      <c r="I4" s="9"/>
-      <c r="J4" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="K4" s="9" t="s">
+      <c r="G4" s="19"/>
+      <c r="H4" s="17"/>
+      <c r="I4" s="19"/>
+      <c r="J4" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="K4" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="L4" s="7" t="s">
+      <c r="L4" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="M4" s="9" t="s">
+      <c r="M4" s="19" t="s">
         <v>69</v>
       </c>
-      <c r="N4" s="7" t="s">
+      <c r="N4" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="O4" s="9"/>
-      <c r="P4" s="7" t="s">
+      <c r="O4" s="19"/>
+      <c r="P4" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="Q4" s="9"/>
-    </row>
-    <row r="5" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="7" t="s">
+      <c r="Q4" s="19"/>
+    </row>
+    <row r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+      <c r="B5" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="C5" s="10"/>
-      <c r="D5" s="7" t="s">
+      <c r="C5" s="20"/>
+      <c r="D5" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="E5" s="10"/>
-      <c r="F5" s="7" t="s">
+      <c r="E5" s="20"/>
+      <c r="F5" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="G5" s="10"/>
-      <c r="H5" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="I5" s="10"/>
-      <c r="J5" s="11" t="s">
+      <c r="G5" s="20"/>
+      <c r="H5" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="I5" s="20"/>
+      <c r="J5" s="21" t="s">
         <v>70</v>
       </c>
-      <c r="K5" s="12"/>
-      <c r="L5" s="7" t="s">
+      <c r="K5" s="22"/>
+      <c r="L5" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="M5" s="10"/>
-      <c r="N5" s="7" t="s">
+      <c r="M5" s="20"/>
+      <c r="N5" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="O5" s="10"/>
-      <c r="P5" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="Q5" s="10"/>
-    </row>
-    <row r="6" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="7" t="s">
+      <c r="O5" s="20"/>
+      <c r="P5" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q5" s="20"/>
+    </row>
+    <row r="6" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+      <c r="B6" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="E6" s="8"/>
-      <c r="F6" s="7" t="s">
+      <c r="E6" s="18"/>
+      <c r="F6" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="G6" s="8" t="s">
+      <c r="G6" s="18" t="s">
         <v>87</v>
       </c>
-      <c r="H6" s="7" t="s">
+      <c r="H6" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="I6" s="8" t="s">
+      <c r="I6" s="18" t="s">
         <v>87</v>
       </c>
-      <c r="J6" s="7" t="s">
+      <c r="J6" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="K6" s="8" t="s">
+      <c r="K6" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="L6" s="7" t="s">
+      <c r="L6" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="M6" s="8"/>
-      <c r="N6" s="7" t="s">
+      <c r="M6" s="18"/>
+      <c r="N6" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="O6" s="8" t="s">
+      <c r="O6" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="P6" s="7" t="s">
+      <c r="P6" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="Q6" s="8" t="s">
+      <c r="Q6" s="18" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="7" t="s">
+    <row r="7" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+      <c r="B7" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="E7" s="9"/>
-      <c r="F7" s="7" t="s">
+      <c r="E7" s="19"/>
+      <c r="F7" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="G7" s="9" t="s">
+      <c r="G7" s="19" t="s">
         <v>88</v>
       </c>
-      <c r="H7" s="7" t="s">
+      <c r="H7" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="I7" s="9" t="s">
+      <c r="I7" s="19" t="s">
         <v>88</v>
       </c>
-      <c r="J7" s="7" t="s">
+      <c r="J7" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="K7" s="9"/>
-      <c r="L7" s="11" t="s">
+      <c r="K7" s="19"/>
+      <c r="L7" s="21" t="s">
         <v>70</v>
       </c>
-      <c r="M7" s="13"/>
-      <c r="N7" s="7" t="s">
+      <c r="M7" s="23"/>
+      <c r="N7" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="O7" s="9"/>
-      <c r="P7" s="7" t="s">
+      <c r="O7" s="19"/>
+      <c r="P7" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="Q7" s="9"/>
-    </row>
-    <row r="8" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="7" t="s">
+      <c r="Q7" s="19"/>
+    </row>
+    <row r="8" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+      <c r="B8" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="C8" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="17" t="s">
         <v>107</v>
       </c>
-      <c r="E8" s="10"/>
-      <c r="F8" s="7" t="s">
+      <c r="E8" s="20"/>
+      <c r="F8" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="G8" s="10" t="s">
+      <c r="G8" s="20" t="s">
         <v>89</v>
       </c>
-      <c r="H8" s="7" t="s">
+      <c r="H8" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="I8" s="10" t="s">
+      <c r="I8" s="20" t="s">
         <v>89</v>
       </c>
-      <c r="J8" s="7" t="s">
+      <c r="J8" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="K8" s="10"/>
-      <c r="L8" s="7" t="s">
+      <c r="K8" s="20"/>
+      <c r="L8" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="M8" s="10"/>
-      <c r="N8" s="7" t="s">
+      <c r="M8" s="20"/>
+      <c r="N8" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="O8" s="10" t="s">
+      <c r="O8" s="20" t="s">
         <v>55</v>
       </c>
-      <c r="P8" s="7" t="s">
+      <c r="P8" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="Q8" s="10" t="s">
+      <c r="Q8" s="20" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="C9" s="8" t="s">
+    <row r="9" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+      <c r="B9" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="C9" s="18" t="s">
         <v>105</v>
       </c>
-      <c r="D9" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="E9" s="8" t="s">
+      <c r="D9" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="E9" s="18" t="s">
         <v>97</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="F9" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="18" t="s">
         <v>90</v>
       </c>
-      <c r="H9" s="7" t="s">
+      <c r="H9" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="I9" s="8" t="s">
+      <c r="I9" s="18" t="s">
         <v>90</v>
       </c>
-      <c r="J9" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="K9" s="8" t="s">
+      <c r="J9" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="K9" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="L9" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="M9" s="8" t="s">
+      <c r="L9" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="M9" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="N9" s="7" t="s">
+      <c r="N9" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="O9" s="8" t="s">
+      <c r="O9" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="P9" s="7" t="s">
+      <c r="P9" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="Q9" s="8" t="s">
+      <c r="Q9" s="18" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="7" t="s">
+    <row r="10" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+      <c r="B10" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="C10" s="9"/>
-      <c r="D10" s="7" t="s">
+      <c r="C10" s="19"/>
+      <c r="D10" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="E10" s="9" t="s">
+      <c r="E10" s="19" t="s">
         <v>98</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="F10" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="G10" s="9"/>
-      <c r="H10" s="7" t="s">
+      <c r="G10" s="19"/>
+      <c r="H10" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="I10" s="9"/>
-      <c r="J10" s="7" t="s">
+      <c r="I10" s="19"/>
+      <c r="J10" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="K10" s="9"/>
-      <c r="L10" s="7" t="s">
+      <c r="K10" s="19"/>
+      <c r="L10" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="M10" s="9" t="s">
+      <c r="M10" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="N10" s="7" t="s">
+      <c r="N10" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="O10" s="9"/>
-      <c r="P10" s="7" t="s">
+      <c r="O10" s="19"/>
+      <c r="P10" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="Q10" s="9"/>
-    </row>
-    <row r="11" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="7" t="s">
+      <c r="Q10" s="19"/>
+    </row>
+    <row r="11" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+      <c r="B11" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="C11" s="10"/>
-      <c r="D11" s="7" t="s">
+      <c r="C11" s="20"/>
+      <c r="D11" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="E11" s="10"/>
-      <c r="F11" s="7" t="s">
+      <c r="E11" s="20"/>
+      <c r="F11" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="G11" s="10" t="s">
+      <c r="G11" s="20" t="s">
         <v>88</v>
       </c>
-      <c r="H11" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="I11" s="10"/>
-      <c r="J11" s="7" t="s">
+      <c r="H11" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="I11" s="20"/>
+      <c r="J11" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="K11" s="10"/>
-      <c r="L11" s="7" t="s">
+      <c r="K11" s="20"/>
+      <c r="L11" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="M11" s="10"/>
-      <c r="N11" s="7" t="s">
+      <c r="M11" s="20"/>
+      <c r="N11" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="O11" s="10"/>
-      <c r="P11" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="Q11" s="10"/>
-    </row>
-    <row r="12" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="C12" s="8" t="s">
+      <c r="O11" s="20"/>
+      <c r="P11" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q11" s="20"/>
+    </row>
+    <row r="12" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+      <c r="B12" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="C12" s="18" t="s">
         <v>106</v>
       </c>
-      <c r="D12" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="E12" s="8" t="s">
+      <c r="D12" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="E12" s="18" t="s">
         <v>99</v>
       </c>
-      <c r="F12" s="7" t="s">
+      <c r="F12" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="G12" s="8" t="s">
+      <c r="G12" s="18" t="s">
         <v>90</v>
       </c>
-      <c r="H12" s="7" t="s">
+      <c r="H12" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="I12" s="8" t="s">
+      <c r="I12" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="J12" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="K12" s="8" t="s">
+      <c r="J12" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="K12" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="L12" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="M12" s="8" t="s">
+      <c r="L12" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="M12" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="N12" s="7" t="s">
+      <c r="N12" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="O12" s="8" t="s">
+      <c r="O12" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="P12" s="7" t="s">
+      <c r="P12" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="Q12" s="8" t="s">
+      <c r="Q12" s="18" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="7" t="s">
+    <row r="13" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+      <c r="B13" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="C13" s="9"/>
-      <c r="D13" s="7" t="s">
+      <c r="C13" s="19"/>
+      <c r="D13" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="E13" s="9" t="s">
+      <c r="E13" s="19" t="s">
         <v>100</v>
       </c>
-      <c r="F13" s="7" t="s">
+      <c r="F13" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="G13" s="9"/>
-      <c r="H13" s="7" t="s">
+      <c r="G13" s="19"/>
+      <c r="H13" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="I13" s="9"/>
-      <c r="J13" s="7" t="s">
+      <c r="I13" s="19"/>
+      <c r="J13" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="K13" s="9"/>
-      <c r="L13" s="7" t="s">
+      <c r="K13" s="19"/>
+      <c r="L13" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="M13" s="9" t="s">
+      <c r="M13" s="19" t="s">
         <v>81</v>
       </c>
-      <c r="N13" s="7" t="s">
+      <c r="N13" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="O13" s="9"/>
-      <c r="P13" s="7" t="s">
+      <c r="O13" s="19"/>
+      <c r="P13" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="Q13" s="9"/>
-    </row>
-    <row r="14" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="7" t="s">
+      <c r="Q13" s="19"/>
+    </row>
+    <row r="14" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+      <c r="B14" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="C14" s="10"/>
-      <c r="D14" s="7" t="s">
+      <c r="C14" s="20"/>
+      <c r="D14" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="E14" s="10"/>
-      <c r="F14" s="11" t="s">
+      <c r="E14" s="20"/>
+      <c r="F14" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="G14" s="12" t="s">
+      <c r="G14" s="22" t="s">
         <v>93</v>
       </c>
-      <c r="H14" s="7" t="s">
+      <c r="H14" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="I14" s="10"/>
-      <c r="J14" s="7" t="s">
+      <c r="I14" s="20"/>
+      <c r="J14" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="K14" s="10"/>
-      <c r="L14" s="7" t="s">
+      <c r="K14" s="20"/>
+      <c r="L14" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="M14" s="10"/>
-      <c r="N14" s="11" t="s">
+      <c r="M14" s="20"/>
+      <c r="N14" s="21" t="s">
         <v>108</v>
       </c>
-      <c r="O14" s="12"/>
-      <c r="P14" s="7" t="s">
+      <c r="O14" s="22"/>
+      <c r="P14" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="Q14" s="10"/>
+      <c r="Q14" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -4437,7 +4477,7 @@
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="76" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="58"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>

--- a/sheets/민요/검수/풍년가.xlsx
+++ b/sheets/민요/검수/풍년가.xlsx
@@ -3930,26 +3930,26 @@
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="14" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="14" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="15" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="14" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="14" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="15" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="14" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="14" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="15" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="14" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="14" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="15" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="14" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="14" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="15" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="14" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="14" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="15" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="14" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="14" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="15" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="14" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="14" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="15" width="6"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="6.0" customHeight="true"/>
-    <row r="2" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="68.97" customHeight="true">
+    <row r="2" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="64.52" customHeight="true">
       <c r="B2" s="16" t="s">
         <v>0</v>
       </c>
@@ -3969,7 +3969,7 @@
       <c r="P2" s="16"/>
       <c r="Q2" s="16"/>
     </row>
-    <row r="3" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+    <row r="3" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="96.05" customHeight="true">
       <c r="B3" s="17" t="s">
         <v>49</v>
       </c>
@@ -4019,7 +4019,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="4" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+    <row r="4" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="96.05" customHeight="true">
       <c r="B4" s="17" t="s">
         <v>49</v>
       </c>
@@ -4059,7 +4059,7 @@
       </c>
       <c r="Q4" s="19"/>
     </row>
-    <row r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+    <row r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="96.05" customHeight="true">
       <c r="B5" s="17" t="s">
         <v>70</v>
       </c>
@@ -4093,7 +4093,7 @@
       </c>
       <c r="Q5" s="20"/>
     </row>
-    <row r="6" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+    <row r="6" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="96.05" customHeight="true">
       <c r="B6" s="17" t="s">
         <v>84</v>
       </c>
@@ -4139,7 +4139,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="7" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+    <row r="7" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="96.05" customHeight="true">
       <c r="B7" s="17" t="s">
         <v>85</v>
       </c>
@@ -4179,7 +4179,7 @@
       </c>
       <c r="Q7" s="19"/>
     </row>
-    <row r="8" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+    <row r="8" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="96.05" customHeight="true">
       <c r="B8" s="17" t="s">
         <v>79</v>
       </c>
@@ -4223,7 +4223,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="9" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+    <row r="9" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="96.05" customHeight="true">
       <c r="B9" s="17" t="s">
         <v>49</v>
       </c>
@@ -4273,7 +4273,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="10" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+    <row r="10" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="96.05" customHeight="true">
       <c r="B10" s="17" t="s">
         <v>76</v>
       </c>
@@ -4311,7 +4311,7 @@
       </c>
       <c r="Q10" s="19"/>
     </row>
-    <row r="11" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+    <row r="11" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="96.05" customHeight="true">
       <c r="B11" s="17" t="s">
         <v>58</v>
       </c>
@@ -4347,7 +4347,7 @@
       </c>
       <c r="Q11" s="20"/>
     </row>
-    <row r="12" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+    <row r="12" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="96.05" customHeight="true">
       <c r="B12" s="17" t="s">
         <v>49</v>
       </c>
@@ -4397,7 +4397,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="13" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+    <row r="13" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="96.05" customHeight="true">
       <c r="B13" s="17" t="s">
         <v>70</v>
       </c>
@@ -4435,7 +4435,7 @@
       </c>
       <c r="Q13" s="19"/>
     </row>
-    <row r="14" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+    <row r="14" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="96.05" customHeight="true">
       <c r="B14" s="17" t="s">
         <v>73</v>
       </c>
@@ -4477,7 +4477,7 @@
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="58"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="62"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
